--- a/demo_data/sectors/hizmet_yazilim/mizan_prior.xlsx
+++ b/demo_data/sectors/hizmet_yazilim/mizan_prior.xlsx
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9125.01</v>
+        <v>9125.02</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1021796.93</v>
+        <v>1021796.94</v>
       </c>
     </row>
     <row r="53">

--- a/demo_data/sectors/hizmet_yazilim/mizan_prior.xlsx
+++ b/demo_data/sectors/hizmet_yazilim/mizan_prior.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-1785403.07</v>
+        <v>5184196.93</v>
       </c>
     </row>
     <row r="54">
@@ -1419,12 +1419,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>622.01</t>
+          <t>740.01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Satılan Hizmet Maliyeti (-)</t>
+          <t>Hizmet Üretim Maliyeti (Operasyon &amp; Doğrudan Giderler)</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1437,16 +1437,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>631.01</t>
+          <t>622.01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pazarlama, Satış ve Dağıtım Giderleri</t>
+          <t>Satılan Hizmet Maliyeti (-)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4791600</v>
+        <v>6969600</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1455,16 +1455,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>632.01</t>
+          <t>631.01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Genel Yönetim Giderleri</t>
+          <t>Pazarlama, Satış ve Dağıtım Giderleri</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3920400</v>
+        <v>4791600</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1473,16 +1473,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>660.01</t>
+          <t>632.01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Finansman Giderleri (Ticari Kredi Faizleri)</t>
+          <t>Genel Yönetim Giderleri</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>387200</v>
+        <v>3920400</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1491,18 +1491,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>660.01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Finansman Giderleri (Ticari Kredi Faizleri)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>387200</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>691.01</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Dönem Kârı Vergi ve Yasal Yükümlülükleri</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C61" t="n">
         <v>484000</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D61" t="n">
         <v>0</v>
       </c>
     </row>
